--- a/q-war/config/General.xlsx
+++ b/q-war/config/General.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Test_Center\Personal_Exp\QWar\q-war\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79F376D2-0DE8-43E1-9FDB-E30244AD1909}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2253637E-24D5-4235-92DC-01FBCC5BD77C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42030" yWindow="2535" windowWidth="25485" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39060" yWindow="1215" windowWidth="20655" windowHeight="17070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>GID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -132,10 +132,6 @@
   </si>
   <si>
     <t>003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>004</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -481,7 +477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -578,7 +574,7 @@
         <v>5</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -598,7 +594,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -618,15 +614,10 @@
         <v>3</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F5">
         <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
